--- a/stories/arbres/ATOM-SEC.PAR.001-14.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-14.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Émilie arrive au square avec papa. Papa montre la fontaine. C'est l'espace montré. Émilie s'approche. L'eau clapote. Elle touche une goutte. Papa s'assoit sur le banc. L'adulte voit Émilie. Émilie reste dans l'espace montré. Papa dit : je te vois. L'adulte voit. Plus tard, papa montre le toboggan bas. Autre lieu, même leçon. C'est encore l'espace montré. Émilie monte les marches. Ses mains tiennent la rampe. Elle glisse. Le plastique est lisse. Elle reste là où papa a dit. Papa la voit. Émilie revient près du banc. L'espace montré, c'est ici. L'adulte voit.</t>
+          <t>Émilie arrive au square avec papa. Papa montre la fontaine. C'est l'espace montré. Émilie s'approche. L'eau clapote. Elle touche une goutte. Papa s'assoit sur le banc. L'adulte voit Émilie. Émilie reste dans l'espace montré. Je te vois. L'adulte voit. Plus tard, papa montre le toboggan bas. Autre lieu, même leçon. C'est encore l'espace montré. Émilie monte les marches. Ses mains tiennent la rampe. Elle glisse. Le plastique est lisse. Elle reste là où papa a dit. Papa la voit. Émilie revient près du banc. L'espace montré, c'est ici. L'adulte voit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Émilie arrive au square avec papa. Papa montre la fontaine. C'est l'espace montré. Émilie s'approche. L'eau clapote. Elle touche une goutte. Papa s'assoit sur le banc. L'adulte voit Émilie. Émilie reste dans l'espace montré.
+papa|Je te vois. L'adulte voit. Plus tard, papa montre le toboggan bas. Autre lieu, même leçon. C'est encore l'espace montré.
+narrateur|Émilie monte les marches. Ses mains tiennent la rampe. Elle glisse. Le plastique est lisse. Elle reste là où papa a dit. Papa la voit. Émilie revient près du banc. L'espace montré, c'est ici. L'adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Émilie joue au square. Où reste-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Émilie est restée dans l'espace montré. À la fontaine, puis au toboggan. L'adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Émilie prend la main de papa. Ils quittent le square.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-14.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-14.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Émilie monte les marches. Ses mains tiennent la rampe. Elle glisse. Le plastique est lisse. Elle reste là où papa a dit. Papa la voit. Émilie revient près du banc. L'espace montré, c'est ici. L'adulte voit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Émilie joue au square. Où reste-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Émilie est restée dans l'espace montré. À la fontaine, puis au toboggan. L'adulte voit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Émilie prend la main de papa. Ils quittent le square.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-14.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-14.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Émilie joue où papa peut voir</t>
+          <t>La fontaine de Victorina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorina touche l'eau de la fontaine puis glisse, dans l'espace que papa a montré.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Émilie arrive au square avec papa. Papa montre la fontaine. C'est l'espace montré. Émilie s'approche. L'eau clapote. Elle touche une goutte. Papa s'assoit sur le banc. L'adulte voit Émilie. Émilie reste dans l'espace montré. Je te vois. L'adulte voit. Plus tard, papa montre le toboggan bas. Autre lieu, même leçon. C'est encore l'espace montré. Émilie monte les marches. Ses mains tiennent la rampe. Elle glisse. Le plastique est lisse. Elle reste là où papa a dit. Papa la voit. Émilie revient près du banc. L'espace montré, c'est ici. L'adulte voit.</t>
+          <t>Une goutte d'eau saute de la fontaine. Elle éclate sur la pierre grise. Le square sent l'eau fraîche. Une pierre lisse brille au soleil. Un banc vert attend à l'ombre. Papa pose le gilet sur le banc. Tu as vu la goutte, Victorina ? Oui, papa. Elle saute. En ce moment, papa montre la fontaine. C'est l'espace montré. Tu joues ici. L'adulte voit. Près de l'eau ? Oui. On reste dans l'espace montré. Victorina s'approche. L'eau clapote. Elle touche une goutte. La goutte est froide et ronde. Papa s'assoit sur le banc vert. L'adulte voit Victorina. Victorina reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Une autre goutte tombe sur sa main. Elle est froide. Oui. Tu joues là où l'adulte a dit. Plus tard, papa montre le toboggan bas. C'est encore l'espace montré. Ici, l'adulte voit. Je peux glisser ? Oui. Tu restes dans l'espace montré. Victorina monte les marches. Ses mains tiennent la rampe. La rampe est lisse et tiède. Elle glisse. Le plastique est lisse. Elle reste là où papa a dit. Papa la voit. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Au toboggan. Bravo, Victorina. Tu as fait du bon travail. Victorina revient près du banc. L'espace montré, c'est ici. L'adulte voit. Tu as fini de glisser ? Oui, papa. Bravo. La fontaine clapote encore. Une goutte sèche sur la pierre. Victorina essuie sa main au gilet. C'est mouillé. Oui. L'eau est fraîche. Elle reste dans l'espace montré. L'adulte voit. Le toboggan bas brille un peu. Victorina touche la rampe encore. C'est lisse. Oui. Tu as glissé dans l'espace montré. Dans l'espace montré. Bravo. Une goutte sèche sur sa manche. Le square sent encore l'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,79 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Émilie arrive au square avec papa. Papa montre la fontaine. C'est l'espace montré. Émilie s'approche. L'eau clapote. Elle touche une goutte. Papa s'assoit sur le banc. L'adulte voit Émilie. Émilie reste dans l'espace montré.
-papa|Je te vois. L'adulte voit. Plus tard, papa montre le toboggan bas. Autre lieu, même leçon. C'est encore l'espace montré.
-narrateur|Émilie monte les marches. Ses mains tiennent la rampe. Elle glisse. Le plastique est lisse. Elle reste là où papa a dit. Papa la voit. Émilie revient près du banc. L'espace montré, c'est ici. L'adulte voit.</t>
+          <t>narrateur|Une goutte d'eau saute de la fontaine.
+narrateur|Elle éclate sur la pierre grise.
+narrateur|Le square sent l'eau fraîche.
+narrateur|Une pierre lisse brille au soleil.
+narrateur|Un banc vert attend à l'ombre.
+narrateur|Papa pose le gilet sur le banc.
+papa|Tu as vu la goutte, Victorina ?
+enfant-f|Oui, papa.
+enfant-f|Elle saute.
+narrateur|En ce moment, papa montre la fontaine.
+papa|C'est l'espace montré.
+papa|Tu joues ici.
+papa|L'adulte voit.
+enfant-f|Près de l'eau ?
+papa|Oui.
+papa|On reste dans l'espace montré.
+narrateur|Victorina s'approche.
+narrateur|L'eau clapote.
+narrateur|Elle touche une goutte.
+narrateur|La goutte est froide et ronde.
+narrateur|Papa s'assoit sur le banc vert.
+narrateur|L'adulte voit Victorina.
+narrateur|Victorina reste dans l'espace montré.
+papa|Je te vois.
+papa|L'adulte voit.
+enfant-f|Tu me vois ?
+papa|Oui.
+narrateur|Une autre goutte tombe sur sa main.
+enfant-f|Elle est froide.
+papa|Oui.
+papa|Tu joues là où l'adulte a dit.
+narrateur|Plus tard, papa montre le toboggan bas.
+papa|C'est encore l'espace montré.
+papa|Ici, l'adulte voit.
+enfant-f|Je peux glisser ?
+papa|Oui.
+papa|Tu restes dans l'espace montré.
+narrateur|Victorina monte les marches.
+narrateur|Ses mains tiennent la rampe.
+narrateur|La rampe est lisse et tiède.
+narrateur|Elle glisse.
+narrateur|Le plastique est lisse.
+narrateur|Elle reste là où papa a dit.
+narrateur|Papa la voit.
+narrateur|L'adulte voit.
+papa|Tu restes là où l'adulte a dit ?
+enfant-f|Oui.
+enfant-f|Au toboggan.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+narrateur|Victorina revient près du banc.
+narrateur|L'espace montré, c'est ici.
+narrateur|L'adulte voit.
+papa|Tu as fini de glisser ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|La fontaine clapote encore.
+narrateur|Une goutte sèche sur la pierre.
+narrateur|Victorina essuie sa main au gilet.
+enfant-f|C'est mouillé.
+papa|Oui.
+papa|L'eau est fraîche.
+narrateur|Elle reste dans l'espace montré.
+narrateur|L'adulte voit.
+narrateur|Le toboggan bas brille un peu.
+narrateur|Victorina touche la rampe encore.
+enfant-f|C'est lisse.
+papa|Oui.
+papa|Tu as glissé dans l'espace montré.
+enfant-f|Dans l'espace montré.
+papa|Bravo.
+narrateur|Une goutte sèche sur sa manche.
+narrateur|Le square sent encore l'eau.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1424,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Émilie joue au square. Où reste-t-elle ?</t>
+          <t>Victorina joue au square. Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1580,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Émilie joue au square. Où reste-t-elle ?</t>
+          <t>narrateur|Victorina joue au square.
+narrateur|Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1609,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Émilie est restée dans l'espace montré. À la fontaine, puis au toboggan. L'adulte voit.</t>
+          <t>Victorina est restée dans l'espace montré. À la fontaine, puis au toboggan. L'adulte voit. Tu es restée dans l'espace montré ? Oui. À la fontaine, puis au toboggan. Bravo. L'adulte voit. La pierre grise brille encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1753,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Émilie est restée dans l'espace montré. À la fontaine, puis au toboggan. L'adulte voit.</t>
+          <t>narrateur|Victorina est restée dans l'espace montré.
+narrateur|À la fontaine, puis au toboggan.
+narrateur|L'adulte voit.
+papa|Tu es restée dans l'espace montré ?
+enfant-f|Oui.
+enfant-f|À la fontaine, puis au toboggan.
+papa|Bravo.
+papa|L'adulte voit.
+narrateur|La pierre grise brille encore.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1789,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Émilie prend la main de papa. Ils quittent le square.</t>
+          <t>Victorina prend la main de papa. Tu as fini près de l'eau ? Oui, papa. Bravo. Ils quittent le square. La fontaine reste derrière eux. Le gilet bleu balance un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1929,13 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Émilie prend la main de papa. Ils quittent le square.</t>
+          <t>narrateur|Victorina prend la main de papa.
+papa|Tu as fini près de l'eau ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|Ils quittent le square.
+narrateur|La fontaine reste derrière eux.
+narrateur|Le gilet bleu balance un peu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une dernière goutte saute. On a glissé. Oui. Dans l'espace montré. Bravo, Victorina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2103,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une dernière goutte saute.
+enfant-f|On a glissé.
+papa|Oui.
+papa|Dans l'espace montré.
+papa|Bravo, Victorina.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-14.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-14.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte d'eau saute de la fontaine. Elle éclate sur la pierre grise. Le square sent l'eau fraîche. Une pierre lisse brille au soleil. Un banc vert attend à l'ombre. Papa pose le gilet sur le banc. Tu as vu la goutte, Victorina ? Oui, papa. Elle saute. En ce moment, papa montre la fontaine. C'est l'espace montré. Tu joues ici. L'adulte voit. Près de l'eau ? Oui. On reste dans l'espace montré. Victorina s'approche. L'eau clapote. Elle touche une goutte. La goutte est froide et ronde. Papa s'assoit sur le banc vert. L'adulte voit Victorina. Victorina reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Une autre goutte tombe sur sa main. Elle est froide. Oui. Tu joues là où l'adulte a dit. Plus tard, papa montre le toboggan bas. C'est encore l'espace montré. Ici, l'adulte voit. Je peux glisser ? Oui. Tu restes dans l'espace montré. Victorina monte les marches. Ses mains tiennent la rampe. La rampe est lisse et tiède. Elle glisse. Le plastique est lisse. Elle reste là où papa a dit. Papa la voit. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Au toboggan. Bravo, Victorina. Tu as fait du bon travail. Victorina revient près du banc. L'espace montré, c'est ici. L'adulte voit. Tu as fini de glisser ? Oui, papa. Bravo. La fontaine clapote encore. Une goutte sèche sur la pierre. Victorina essuie sa main au gilet. C'est mouillé. Oui. L'eau est fraîche. Elle reste dans l'espace montré. L'adulte voit. Le toboggan bas brille un peu. Victorina touche la rampe encore. C'est lisse. Oui. Tu as glissé dans l'espace montré. Dans l'espace montré. Bravo. Une goutte sèche sur sa manche. Le square sent encore l'eau.</t>
+          <t>Une goutte d'eau saute de la fontaine. Elle éclate sur la pierre grise. Le square sent l'eau fraîche. Une pierre lisse brille au soleil. Un banc vert attend à l'ombre. Papa pose le gilet sur le banc. Tu as vu la goutte, Victorina ? Oui, papa. Elle saute. En ce moment, papa montre la fontaine. C'est l'espace montré. Tu joues ici. L'adulte voit. Près de l'eau ? Oui. On reste dans l'espace montré. Victorina s'approche. L'eau clapote. Elle touche une goutte. La goutte est froide et ronde. Papa s'assoit sur le banc vert. L'adulte voit Victorina. Victorina reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Une autre goutte tombe sur sa main. Elle est froide. Oui. Tu joues là où l'adulte a dit. Plus tard, papa montre le toboggan bas. C'est encore l'espace montré. Ici, l'adulte voit. Je peux glisser ? Oui. Tu restes dans l'espace montré. Victorina monte les marches. Ses mains tiennent la rampe. La rampe est lisse et tiède. Elle glisse. Le plastique est lisse. Elle reste là où papa a dit. Papa la voit. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Au toboggan. Bravo, Victorina. Victorina revient près du banc. L'espace montré, c'est ici. L'adulte voit. Tu as fini de glisser ? Oui, papa. Bravo. La fontaine clapote encore. Une goutte sèche sur la pierre. Victorina essuie sa main au gilet. C'est mouillé. Oui. L'eau est fraîche. Elle reste dans l'espace montré. L'adulte voit. Le toboggan bas brille un peu. Victorina touche la rampe encore. C'est lisse. Oui. Tu as glissé dans l'espace montré. Dans l'espace montré. Bravo. Une goutte sèche sur sa manche. Le square sent encore l'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Émilie arrive au square avec papa. Papa montre la fontaine. C'est l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Émilie s'approche. L'eau clapote. Elle touche une goutte. Papa s'assoit sur le banc. L'adulte voit Émilie. Émilie reste dans l'espace montré. Papa dit : je te vois. L'adulte voit. Plus tard, papa montre le toboggan bas. Autre lieu, même leçon. C'est encore l'espace montré. Émilie monte les marches. Ses mains tiennent la rampe. Elle glisse. Le plastique est lisse. Elle reste là où papa a dit. Papa la voit. Émilie revient près du banc. L'espace montré, c'est ici. L'adulte voit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une goutte d'eau saute de la fontaine. Elle éclate sur la pierre grise. Le square sent l'eau fraîche. Une pierre lisse brille au soleil. Un banc vert attend à l'ombre. Papa pose le gilet sur le banc. Tu as vu la goutte, Victorina ? Oui, papa. Elle saute. En ce moment, papa montre la fontaine. C'est l'espace montré. Tu joues ici. L'adulte voit. Près de l'eau ? Oui. On reste dans l'espace montré. Victorina s'approche. L'eau clapote. Elle touche une goutte. La goutte est froide et ronde. Papa s'assoit sur le banc vert. L'adulte voit Victorina. Victorina reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Une autre goutte tombe sur sa main. Elle est froide. Oui. Tu joues là où l'adulte a dit. Plus tard, papa montre le toboggan bas. C'est encore l'espace montré. Ici, l'adulte voit. Je peux glisser ? Oui. Tu restes dans l'espace montré. Victorina monte les marches. Ses mains tiennent la rampe. La rampe est lisse et tiède. Elle glisse. Le plastique est lisse. Elle reste là où papa a dit. Papa la voit. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Au toboggan. Bravo, Victorina. Victorina revient près du banc. L'espace montré, c'est ici. L'adulte voit. Tu as fini de glisser ? Oui, papa. Bravo. La fontaine clapote encore. Une goutte sèche sur la pierre. Victorina essuie sa main au gilet. C'est mouillé. Oui. L'eau est fraîche. Elle reste dans l'espace montré. L'adulte voit. Le toboggan bas brille un peu. Victorina touche la rampe encore. C'est lisse. Oui. Tu as glissé dans l'espace montré. Dans l'espace montré. Bravo. Une goutte sèche sur sa manche. Le square sent encore l'eau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1373,7 +1373,6 @@
 enfant-f|Oui.
 enfant-f|Au toboggan.
 papa|Bravo, Victorina.
-papa|Tu as fait du bon travail.
 narrateur|Victorina revient près du banc.
 narrateur|L'espace montré, c'est ici.
 narrateur|L'adulte voit.
@@ -1399,7 +1398,6 @@
 narrateur|Le square sent encore l'eau.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1429,7 +1427,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Émilie joue au square. Où reste-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina joue au square. Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1584,7 +1582,6 @@
 narrateur|Où reste-t-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1614,7 +1611,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Émilie est restée dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. À la fontaine, puis au toboggan. L'adulte voit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina est restée dans l'espace montré. À la fontaine, puis au toboggan. L'adulte voit. Tu es restée dans l'espace montré ? Oui. À la fontaine, puis au toboggan. Bravo. L'adulte voit. La pierre grise brille encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1764,7 +1761,6 @@
 narrateur|La pierre grise brille encore.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1794,7 +1790,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Émilie prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils quittent le square.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina prend la main de papa. Tu as fini près de l'eau ? Oui, papa. Bravo. Ils quittent le square. La fontaine reste derrière eux. Le gilet bleu balance un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1938,7 +1934,6 @@
 narrateur|Le gilet bleu balance un peu.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1963,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Une dernière goutte saute. On a glissé. Oui. Dans l'espace montré. Bravo, Victorina. L'histoire est finie.</t>
+          <t>Une dernière goutte saute. On a glissé. Oui. Dans l'espace montré. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une dernière goutte saute. On a glissé. Oui. Dans l'espace montré. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2107,11 +2102,9 @@
 enfant-f|On a glissé.
 papa|Oui.
 papa|Dans l'espace montré.
-papa|Bravo, Victorina.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Victorina.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2130,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-14.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-14.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Émilie, papa</t>
+          <t>Victorina, papa</t>
         </is>
       </c>
     </row>
